--- a/data/trans_bre/IP1020-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,0</t>
+          <t>-4,74; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 1,41</t>
+          <t>-8,67; 1,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,0</t>
+          <t>-5,85; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 4,27</t>
+          <t>-10,15; 4,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-90,19; 78,12</t>
+          <t>-89,62; 81,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-93,36; 317,98</t>
+          <t>-91,59; 273,45</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,1</t>
+          <t>-0,95; 1,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,86</t>
+          <t>0,15; 2,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,74</t>
+          <t>-0,77; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,86</t>
+          <t>-1,92; 1,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,59; 256,8</t>
+          <t>-70,86; 292,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 810,71</t>
+          <t>-4,87; 796,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 264,82</t>
+          <t>-49,47; 223,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 84,74</t>
+          <t>-48,59; 90,57</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,8</t>
+          <t>-0,79; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,79</t>
+          <t>0,29; 5,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,23</t>
+          <t>-4,75; -0,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,02</t>
+          <t>-1,99; 4,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,07; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 432,91</t>
+          <t>-57,57; 460,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,67</t>
+          <t>-0,83; 0,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,38</t>
+          <t>-0,02; 2,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,6</t>
+          <t>-1,62; 0,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,88</t>
+          <t>-1,47; 1,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,83; 132,56</t>
+          <t>-70,72; 151,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 258,76</t>
+          <t>-3,96; 262,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 61,85</t>
+          <t>-65,28; 51,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,81; 71,38</t>
+          <t>-36,94; 78,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 0,0</t>
+          <t>-6,2; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 1,51</t>
+          <t>-8,61; 1,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 0,0</t>
+          <t>-6,82; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 4,43</t>
+          <t>-10,29; 4,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 81,67</t>
+          <t>-90,25; 97,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-91,59; 273,45</t>
+          <t>-89,76; 350,68</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,18</t>
+          <t>-0,92; 1,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,93</t>
+          <t>0,17; 2,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,72</t>
+          <t>-0,8; 1,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,99</t>
+          <t>-2,06; 2,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,86; 292,4</t>
+          <t>-70,14; 242,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 796,21</t>
+          <t>-3,07; 666,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 223,59</t>
+          <t>-46,86; 248,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 90,57</t>
+          <t>-50,77; 90,83</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,48</t>
+          <t>-0,78; 1,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,94</t>
+          <t>0,25; 5,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; -0,12</t>
+          <t>-4,94; -0,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,94</t>
+          <t>-1,98; 4,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>-49,61; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,57; 460,21</t>
+          <t>-58,34; 430,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,71</t>
+          <t>-0,81; 0,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,44</t>
+          <t>0,08; 2,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,57</t>
+          <t>-1,44; 0,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,83</t>
+          <t>-1,53; 1,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 151,7</t>
+          <t>-65,97; 150,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 262,11</t>
+          <t>-1,41; 255,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 51,53</t>
+          <t>-63,25; 55,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 78,65</t>
+          <t>-38,94; 65,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>-1,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-33,5%</t>
+          <t>-28,51%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,0</t>
+          <t>-5,44; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 1,55</t>
+          <t>-8,72; 1,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 0,0</t>
+          <t>-6,69; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 4,4</t>
+          <t>-10,27; 5,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-90,25; 97,8</t>
+          <t>-90,19; 78,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-89,76; 350,68</t>
+          <t>-93,02; 339,48</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,06%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,11</t>
+          <t>-0,93; 1,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,91</t>
+          <t>0,2; 2,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,7</t>
+          <t>-0,71; 1,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,02</t>
+          <t>-2,24; 2,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,14; 242,86</t>
+          <t>-74,59; 256,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 666,26</t>
+          <t>-6,59; 810,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 248,75</t>
+          <t>-41,36; 264,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 90,83</t>
+          <t>-51,4; 98,85</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,47</t>
+          <t>-0,76; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,95</t>
+          <t>0,33; 5,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,39</t>
+          <t>-4,91; -0,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,86</t>
+          <t>-2,44; 5,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,61; —</t>
+          <t>-62,07; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 75,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 430,85</t>
+          <t>-61,49; 406,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,75</t>
+          <t>-0,9; 0,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,4</t>
+          <t>0,03; 2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,65</t>
+          <t>-1,34; 0,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,77</t>
+          <t>-1,39; 2,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 150,4</t>
+          <t>-70,83; 132,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 255,59</t>
+          <t>-1,33; 258,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 55,88</t>
+          <t>-62,44; 61,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 65,68</t>
+          <t>-35,34; 78,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-51,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-28,51%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.558238376351016</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.016297975270693</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.934616414072823</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.879218169023462</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.5104706676052404</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2850951112001978</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,44; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,72; 1,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,69; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-10,27; 5,32</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-90,19; 78,12</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-93,02; 339,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.437846745149337</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.723095777940983</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.687239124604425</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-10.26957686959848</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.9019492983488199</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.9302103301281814</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.40837361164549</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.32356716379648</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>0.7812158607313263</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>3.394766205275753</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>166,2%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,93; 1,1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 2,86</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,71; 1,74</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,24; 2,19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-74,59; 256,8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 810,71</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-41,36; 264,82</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-51,4; 98,85</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.04633881575764453</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.434168698820032</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4620761714945356</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.1855113851748483</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04909611428938967</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.662027457752942</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3724753826721365</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.05816811638233069</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>326,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-74,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42,47%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.930178632414415</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1955833876626792</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.7079225066765489</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.235792507054916</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7458659643122676</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.06593520901276087</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4135516313230723</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5139937833317813</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 1,8</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,33; 5,79</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,91; -0,23</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,44; 5,04</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-62,07; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 75,81</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-61,49; 406,08</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.099169054170067</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.863879334731068</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.73509501640966</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.189359331701307</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.567972563395255</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>8.10705739651628</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.648221106704759</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.9884944348422644</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +811,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-11,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-22,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.3500084063548991</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.448774458535284</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.12184351790824</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.254913737507928</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.92585307665632</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>3.261916596810551</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.7485056275480836</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.4247439034589229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 0,67</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 2,38</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 0,6</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,39; 2,14</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-70,83; 132,56</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 258,76</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-62,44; 61,85</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-35,34; 78,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.7636126503765893</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3338699067136098</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.911463219224876</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.44095244747117</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.6207128708659411</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6149075392965546</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.799885172699525</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.788302352725533</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.2298280974988436</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.044084166271256</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>0.7581281629120659</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>4.060774920181859</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.102752014451353</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.184474926847729</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3893560508871737</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.2652644558786554</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1149592089930809</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.8454119599696299</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.2282550770948683</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.07783025778575327</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.8989695403122309</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.02988378453840468</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.337781079538165</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.394896372543472</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7082555590981157</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.01328883540247712</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6243521772745275</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3534163681858337</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6742514860364528</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.381575582291107</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6014174259371712</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.143342974809643</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.325598549031524</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.587554194522778</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6185422157354691</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.7883483014593393</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1003,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
